--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813057EA-574E-4FE0-932D-ACD637894B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD762849-8BF2-4DB2-AC8E-89343F86BB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="30630" yWindow="195" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>J'ai ajouter la connexion et j'ai eu un gros problème avec vscode ce qui ma fais perdre beaucoup de temps</t>
+  </si>
+  <si>
+    <t>J'ai ajouter la création de compte</t>
+  </si>
+  <si>
+    <t>J'ai ajouter le hash et le sel</t>
+  </si>
+  <si>
+    <t>J'ai ajouter le poivre</t>
+  </si>
+  <si>
+    <t>J'ai ajouter token jwt</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1165,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>90</c:v>
@@ -2008,10 +2020,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3</c:v>
+                  <c:v>0.54014598540145986</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0.13138686131386862</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4249,7 +4261,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>7 heures 30 minutes</v>
+        <v>11 heures 25 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4264,15 +4276,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>450</v>
+        <v>685</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4391,15 +4403,25 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="62" t="str">
+      <c r="A10" s="62">
         <f>IF(ISBLANK(B10),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B10))</f>
-        <v/>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="B10" s="30">
+        <v>46113</v>
+      </c>
+      <c r="C10" s="31">
+        <v>1</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="G10" s="39"/>
       <c r="M10" t="s">
         <v>15</v>
@@ -4412,15 +4434,25 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="str">
+      <c r="A11" s="63">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
-        <v/>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="B11" s="34">
+        <v>46113</v>
+      </c>
+      <c r="C11" s="35">
+        <v>1</v>
+      </c>
+      <c r="D11" s="36">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="G11" s="40"/>
       <c r="M11" t="s">
         <v>16</v>
@@ -4433,15 +4465,23 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="62" t="str">
+      <c r="A12" s="62">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="30"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46113</v>
+      </c>
       <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="23"/>
+      <c r="D12" s="32">
+        <v>45</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>36</v>
+      </c>
       <c r="G12" s="39"/>
       <c r="M12" t="s">
         <v>17</v>
@@ -4454,15 +4494,25 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="str">
+      <c r="A13" s="63">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="B13" s="34">
+        <v>46113</v>
+      </c>
+      <c r="C13" s="35">
+        <v>1</v>
+      </c>
+      <c r="D13" s="36">
+        <v>0</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="G13" s="40"/>
       <c r="N13">
         <v>6</v>
@@ -10894,15 +10944,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>370</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10910,11 +10960,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>2 h 15 min</v>
+        <v>6 h 10 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.3</v>
+        <v>0.54014598540145986</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10951,7 +11001,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.13138686131386862</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11024,7 +11074,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.5</v>
+        <v>0.32846715328467152</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11040,26 +11090,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>450</v>
+        <v>685</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>7 h 30 min</v>
+        <v>11 h 25 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>8.3333333333333329E-2</v>
+        <v>0.12685185185185185</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11098,17 +11148,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11297,6 +11336,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11307,17 +11357,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11336,6 +11375,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD762849-8BF2-4DB2-AC8E-89343F86BB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07687469-944A-417F-B8F4-7147357E3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30630" yWindow="195" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="7395" yWindow="1110" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -155,6 +155,15 @@
   </si>
   <si>
     <t>J'ai ajouter token jwt</t>
+  </si>
+  <si>
+    <t>J'ai changer le token et le pepper dans le fichier .env car je les avais mis dans AuthController</t>
+  </si>
+  <si>
+    <t>J'ai ajouter les roles dans le token jwt et protégé les routes admins</t>
+  </si>
+  <si>
+    <t>Je suis entrain d'essayer de afficher les infos du compte connecter sur profile</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1174,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>370</c:v>
+                  <c:v>595</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>90</c:v>
@@ -2020,10 +2029,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.54014598540145986</c:v>
+                  <c:v>0.65384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13138686131386862</c:v>
+                  <c:v>9.8901098901098897E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4261,7 +4270,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>11 heures 25 minutes</v>
+        <v>15 heures 10 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4276,15 +4285,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>685</v>
+        <v>910</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4522,15 +4531,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="str">
+      <c r="A14" s="62">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23"/>
+        <v>17</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46134</v>
+      </c>
+      <c r="C14" s="31">
+        <v>1</v>
+      </c>
+      <c r="D14" s="32">
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="G14" s="39"/>
       <c r="N14">
         <v>7</v>
@@ -4540,15 +4559,25 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="str">
+      <c r="A15" s="63">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="23"/>
+        <v>17</v>
+      </c>
+      <c r="B15" s="34">
+        <v>46134</v>
+      </c>
+      <c r="C15" s="35">
+        <v>2</v>
+      </c>
+      <c r="D15" s="36">
+        <v>0</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>39</v>
+      </c>
       <c r="G15" s="40"/>
       <c r="N15">
         <v>8</v>
@@ -4558,15 +4587,23 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="62" t="str">
+      <c r="A16" s="62">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="30"/>
+        <v>17</v>
+      </c>
+      <c r="B16" s="30">
+        <v>46134</v>
+      </c>
       <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="23"/>
+      <c r="D16" s="32">
+        <v>45</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>40</v>
+      </c>
       <c r="G16" s="39"/>
       <c r="O16">
         <v>40</v>
@@ -10944,15 +10981,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>370</v>
+        <v>595</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10960,11 +10997,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>6 h 10 min</v>
+        <v>9 h 55 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.54014598540145986</v>
+        <v>0.65384615384615385</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11001,7 +11038,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>0.13138686131386862</v>
+        <v>9.8901098901098897E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11074,7 +11111,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.32846715328467152</v>
+        <v>0.24725274725274726</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11090,26 +11127,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>685</v>
+        <v>910</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>11 h 25 min</v>
+        <v>15 h 10 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.12685185185185185</v>
+        <v>0.16851851851851851</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11148,6 +11185,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11336,17 +11384,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11357,6 +11394,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11375,17 +11423,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07687469-944A-417F-B8F4-7147357E3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA044C95-B453-4DCC-8302-E6564674719C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7395" yWindow="1110" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA044C95-B453-4DCC-8302-E6564674719C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3A5D0-2874-412F-ADF2-635CE1313321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7395" yWindow="1110" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="3630" yWindow="1110" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -164,6 +164,21 @@
   </si>
   <si>
     <t>Je suis entrain d'essayer de afficher les infos du compte connecter sur profile</t>
+  </si>
+  <si>
+    <t>J'ai réglé le problème de la page profile qui n'affichait pas les infos du compte connecter</t>
+  </si>
+  <si>
+    <t>J'ai ajouter le https avec mkcert</t>
+  </si>
+  <si>
+    <t>J'ai ajouter une politique de mot de passe avec un indicateur de force</t>
+  </si>
+  <si>
+    <t>J'ai ajouter le refresh token</t>
+  </si>
+  <si>
+    <t>J'ai ajouter une limite de 5 essaye pour se connecter si c'est depasser on dois attendre 1 minute</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1189,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>595</c:v>
+                  <c:v>820</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>90</c:v>
@@ -2029,10 +2044,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.65384615384615385</c:v>
+                  <c:v>0.72246696035242286</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.8901098901098897E-2</c:v>
+                  <c:v>7.9295154185022032E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4270,7 +4285,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>15 heures 10 minutes</v>
+        <v>18 heures 55 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4285,15 +4300,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>190</v>
+        <v>355</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>910</v>
+        <v>1135</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4610,72 +4625,114 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="63" t="str">
+      <c r="A17" s="63">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="34"/>
+        <v>18</v>
+      </c>
+      <c r="B17" s="34">
+        <v>46141</v>
+      </c>
       <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="23"/>
+      <c r="D17" s="36">
+        <v>55</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="G17" s="40"/>
       <c r="O17">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="62" t="str">
+      <c r="A18" s="62">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="B18" s="30">
+        <v>46141</v>
+      </c>
+      <c r="C18" s="31">
+        <v>1</v>
+      </c>
+      <c r="D18" s="32">
+        <v>0</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>42</v>
+      </c>
       <c r="G18" s="39"/>
       <c r="O18">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="63" t="str">
+      <c r="A19" s="63">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="34"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="34">
+        <v>46141</v>
+      </c>
       <c r="C19" s="35"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="23"/>
+      <c r="D19" s="36">
+        <v>30</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>43</v>
+      </c>
       <c r="G19" s="40"/>
       <c r="O19">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="62" t="str">
+      <c r="A20" s="62">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="30"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="30">
+        <v>46141</v>
+      </c>
       <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="23"/>
+      <c r="D20" s="32">
+        <v>55</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>44</v>
+      </c>
       <c r="G20" s="39"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="63" t="str">
+      <c r="A21" s="63">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="34"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="34">
+        <v>46141</v>
+      </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="23"/>
+      <c r="D21" s="36">
+        <v>25</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>45</v>
+      </c>
       <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -10981,15 +11038,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>595</v>
+        <v>820</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10997,11 +11054,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>9 h 55 min</v>
+        <v>13 h 40 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.65384615384615385</v>
+        <v>0.72246696035242286</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11038,7 +11095,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>9.8901098901098897E-2</v>
+        <v>7.9295154185022032E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11111,7 +11168,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.24725274725274726</v>
+        <v>0.19823788546255505</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11127,26 +11184,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>190</v>
+        <v>355</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>910</v>
+        <v>1135</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>15 h 10 min</v>
+        <v>18 h 55 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.16851851851851851</v>
+        <v>0.2101851851851852</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11185,17 +11242,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11384,6 +11430,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11394,17 +11451,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11423,6 +11469,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3A5D0-2874-412F-ADF2-635CE1313321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EC6580-8B16-4CEE-9D07-30CE50A37397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="1110" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>J'ai ajouter une limite de 5 essaye pour se connecter si c'est depasser on dois attendre 1 minute</t>
+  </si>
+  <si>
+    <t>J'ai avancé mon rapport</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1198,7 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>225</c:v>
@@ -2044,13 +2047,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.72246696035242286</c:v>
+                  <c:v>0.6029411764705882</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.9295154185022032E-2</c:v>
+                  <c:v>6.6176470588235295E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.16544117647058823</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4285,7 +4288,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>18 heures 55 minutes</v>
+        <v>22 heures 40 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4300,15 +4303,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>780</v>
+        <v>960</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1135</v>
+        <v>1360</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4736,15 +4739,25 @@
       <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="str">
+      <c r="A22" s="62">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="30">
+        <v>46118</v>
+      </c>
+      <c r="C22" s="31">
+        <v>3</v>
+      </c>
+      <c r="D22" s="32">
+        <v>45</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="G22" s="39"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -11058,7 +11071,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.72246696035242286</v>
+        <v>0.6029411764705882</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11095,7 +11108,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>7.9295154185022032E-2</v>
+        <v>6.6176470588235295E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11112,15 +11125,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11128,11 +11141,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 00 min</v>
+        <v>3 h 45 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.16544117647058823</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11168,7 +11181,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.19823788546255505</v>
+        <v>0.16544117647058823</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11184,26 +11197,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>780</v>
+        <v>960</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1135</v>
+        <v>1360</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>18 h 55 min</v>
+        <v>22 h 40 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.2101851851851852</v>
+        <v>0.25185185185185183</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11242,6 +11255,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11430,17 +11454,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11451,6 +11464,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11469,17 +11493,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EC6580-8B16-4CEE-9D07-30CE50A37397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052B474F-DBFC-497A-8627-6D3CCD8650CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -182,6 +182,18 @@
   </si>
   <si>
     <t>J'ai avancé mon rapport</t>
+  </si>
+  <si>
+    <t>J'ai ajouter la gestion des exceptions pour que cela retourne peu d'information</t>
+  </si>
+  <si>
+    <t>J'ai fais la partie de l'audit fix avec npm et je l'ai documenter dans mon rapport</t>
+  </si>
+  <si>
+    <t>J'ai fais l'évaluation du projet a 80%</t>
+  </si>
+  <si>
+    <t>J'ai avancé sur le rapport</t>
   </si>
 </sst>
 </file>
@@ -1189,16 +1201,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>820</c:v>
+                  <c:v>910</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>225</c:v>
+                  <c:v>345</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>225</c:v>
@@ -2044,16 +2056,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.4637223974763408E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6029411764705882</c:v>
+                  <c:v>0.57413249211356465</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.6176470588235295E-2</c:v>
+                  <c:v>5.6782334384858045E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16544117647058823</c:v>
+                  <c:v>0.21766561514195584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4288,7 +4300,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>22 heures 40 minutes</v>
+        <v>26 heures 25 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4303,15 +4315,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>960</v>
+        <v>1140</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1360</v>
+        <v>1585</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4741,10 +4753,10 @@
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" s="30">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C22" s="31">
         <v>3</v>
@@ -4761,51 +4773,87 @@
       <c r="G22" s="39"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="str">
+      <c r="A23" s="63">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="34">
+        <v>46155</v>
+      </c>
+      <c r="C23" s="35">
+        <v>1</v>
+      </c>
+      <c r="D23" s="36">
+        <v>0</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="G23" s="40"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="str">
+      <c r="A24" s="62">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="30"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="30">
+        <v>46155</v>
+      </c>
       <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="32">
+        <v>30</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>48</v>
+      </c>
       <c r="G24" s="39"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="63" t="str">
+      <c r="A25" s="63">
         <f>IF(ISBLANK(B25),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="34"/>
+        <v>20</v>
+      </c>
+      <c r="B25" s="34">
+        <v>46155</v>
+      </c>
       <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="23"/>
+      <c r="D25" s="36">
+        <v>15</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="G25" s="40"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="62" t="str">
+      <c r="A26" s="62">
         <f>IF(ISBLANK(B26),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="30">
+        <v>46155</v>
+      </c>
+      <c r="C26" s="31">
+        <v>2</v>
+      </c>
+      <c r="D26" s="32">
+        <v>0</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -11018,11 +11066,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11030,11 +11078,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>0 h 00 min</v>
+        <v>0 h 15 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0</v>
+        <v>9.4637223974763408E-3</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11051,15 +11099,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>910</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11067,11 +11115,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>13 h 40 min</v>
+        <v>15 h 10 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.6029411764705882</v>
+        <v>0.57413249211356465</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11108,7 +11156,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>6.6176470588235295E-2</v>
+        <v>5.6782334384858045E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11125,7 +11173,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
@@ -11133,7 +11181,7 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11141,11 +11189,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>3 h 45 min</v>
+        <v>5 h 45 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.16544117647058823</v>
+        <v>0.21766561514195584</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11181,7 +11229,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.16544117647058823</v>
+        <v>0.14195583596214512</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11197,26 +11245,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>960</v>
+        <v>1140</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1360</v>
+        <v>1585</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>22 h 40 min</v>
+        <v>26 h 25 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.25185185185185183</v>
+        <v>0.29351851851851851</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11255,17 +11303,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11454,6 +11491,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11464,17 +11512,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11493,6 +11530,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052B474F-DBFC-497A-8627-6D3CCD8650CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1946D72-9C22-4D88-A5DB-C4455B82317B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="3630" yWindow="1110" windowWidth="23070" windowHeight="13395" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>J'ai avancé sur le rapport</t>
+  </si>
+  <si>
+    <t>TEST aural</t>
+  </si>
+  <si>
+    <t>J'ai fini mon rapport</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1207,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>910</c:v>
@@ -1210,7 +1216,7 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>345</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>225</c:v>
@@ -2056,16 +2062,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9.4637223974763408E-3</c:v>
+                  <c:v>3.3149171270718231E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.57413249211356465</c:v>
+                  <c:v>0.50276243093922657</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.6782334384858045E-2</c:v>
+                  <c:v>4.9723756906077346E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21766561514195584</c:v>
+                  <c:v>0.29005524861878451</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4300,7 +4306,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>26 heures 25 minutes</v>
+        <v>30 heures 10 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4315,15 +4321,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>1140</v>
+        <v>1320</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1585</v>
+        <v>1810</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4857,27 +4863,45 @@
       <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="63" t="str">
+      <c r="A27" s="63">
         <f>IF(ISBLANK(B27),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="34"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="34">
+        <v>46162</v>
+      </c>
       <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="23"/>
+      <c r="D27" s="36">
+        <v>45</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>51</v>
+      </c>
       <c r="G27" s="40"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="62" t="str">
+      <c r="A28" s="62">
         <f>IF(ISBLANK(B28),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="22"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="30">
+        <v>46162</v>
+      </c>
+      <c r="C28" s="31">
+        <v>3</v>
+      </c>
+      <c r="D28" s="32">
+        <v>0</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="G28" s="39"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -11066,11 +11090,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11078,11 +11102,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>0 h 15 min</v>
+        <v>1 h 00 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>9.4637223974763408E-3</v>
+        <v>3.3149171270718231E-2</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11119,7 +11143,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.57413249211356465</v>
+        <v>0.50276243093922657</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11156,7 +11180,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>5.6782334384858045E-2</v>
+        <v>4.9723756906077346E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11173,7 +11197,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
@@ -11181,7 +11205,7 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>345</v>
+        <v>525</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11189,11 +11213,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>5 h 45 min</v>
+        <v>8 h 45 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.21766561514195584</v>
+        <v>0.29005524861878451</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11229,7 +11253,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.14195583596214512</v>
+        <v>0.12430939226519337</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11245,26 +11269,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>1140</v>
+        <v>1320</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1585</v>
+        <v>1810</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>26 h 25 min</v>
+        <v>30 h 10 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.29351851851851851</v>
+        <v>0.3351851851851852</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11303,6 +11327,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11491,17 +11526,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11512,6 +11536,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11530,17 +11565,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Doc/Journal-de-Travail_PeltierThomas.xlsx
+++ b/Doc/Journal-de-Travail_PeltierThomas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\secured_webshop\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1946D72-9C22-4D88-A5DB-C4455B82317B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F73B080-4B22-4AA2-8164-7D4E4115CE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3630" yWindow="1110" windowWidth="23070" windowHeight="13395" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>J'ai fini mon rapport</t>
+  </si>
+  <si>
+    <t>J'ai continué mon rapport</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>525</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>225</c:v>
@@ -2062,16 +2065,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.3149171270718231E-2</c:v>
+                  <c:v>2.9484029484029485E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.50276243093922657</c:v>
+                  <c:v>0.44717444717444715</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9723756906077346E-2</c:v>
+                  <c:v>4.4226044226044224E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29005524861878451</c:v>
+                  <c:v>0.36855036855036855</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4306,7 +4309,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>30 heures 10 minutes</v>
+        <v>33 heures 55 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4321,15 +4324,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>1320</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1810</v>
+        <v>2035</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4900,20 +4903,30 @@
         <v>16</v>
       </c>
       <c r="F28" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="39"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="63">
+        <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
+        <v>21</v>
+      </c>
+      <c r="B29" s="34">
+        <v>46162</v>
+      </c>
+      <c r="C29" s="35">
+        <v>3</v>
+      </c>
+      <c r="D29" s="36">
+        <v>45</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="39"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="63" t="str">
-        <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="22"/>
       <c r="G29" s="40"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -11106,7 +11119,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>3.3149171270718231E-2</v>
+        <v>2.9484029484029485E-2</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11143,7 +11156,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.50276243093922657</v>
+        <v>0.44717444717444715</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11180,7 +11193,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>4.9723756906077346E-2</v>
+        <v>4.4226044226044224E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11197,15 +11210,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>525</v>
+        <v>750</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11213,11 +11226,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>8 h 45 min</v>
+        <v>12 h 30 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.29005524861878451</v>
+        <v>0.36855036855036855</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11253,7 +11266,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.12430939226519337</v>
+        <v>0.11056511056511056</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>17</v>
@@ -11269,26 +11282,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>1320</v>
+        <v>1500</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1810</v>
+        <v>2035</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>30 h 10 min</v>
+        <v>33 h 55 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.3351851851851852</v>
+        <v>0.37685185185185183</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>28</v>
@@ -11327,17 +11340,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5bf905bc6027d3a3176cf398b6d748a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdc8923a5f0a5cb2ad217e59a32ed26c" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11526,6 +11528,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11536,17 +11549,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB23EBB1-226D-48F9-BD4F-72DBF2899D35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11565,6 +11567,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
